--- a/buildplan_generator/output/25-076 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-076 GENERATED BUILD PLAN.xlsx
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-109, 25-034, 25-097, 25-096, 25-094</t>
+          <t>23-057, 23-059, 23-058, 25-010, 23-061</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +720,8 @@
       <c r="E9" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>3</v>
+      <c r="F9" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>4</v>
+      <c r="F10" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>2.0-6.0</t>
+          <t>ratio=1.00 (0.71-1.50)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -813,8 +811,8 @@
       <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>6</v>
+      <c r="F12" s="9" t="n">
+        <v>1.6</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -823,7 +821,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>2.5-8.0</t>
+          <t>ratio=0.80 (0.62-1.21)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -851,16 +849,16 @@
         <v>1</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>0.8-4.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -904,8 +902,8 @@
       <c r="E15" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>3</v>
+      <c r="F15" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -914,7 +912,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.10)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -958,7 +956,7 @@
       <c r="E17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -968,7 +966,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -996,7 +994,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1005,7 +1003,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>6.0-6.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1050,12 +1048,12 @@
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1082,8 +1080,8 @@
       <c r="E21" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="9" t="n">
-        <v>9</v>
+      <c r="F21" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1092,7 +1090,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-64.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1119,8 +1117,8 @@
       <c r="E22" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="9" t="n">
-        <v>12</v>
+      <c r="F22" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1129,7 +1127,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-74.2</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1156,17 +1154,17 @@
       <c r="E23" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1191,17 +1189,15 @@
         </is>
       </c>
       <c r="E24" s="8" t="n"/>
-      <c r="F24" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1229,16 +1225,16 @@
         <v>2</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-114.5</t>
+          <t>ratio=1.17 (1.00-1.17)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1282,17 +1278,17 @@
       <c r="E27" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="11" t="n">
-        <v>1</v>
+      <c r="F27" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=0.83 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1319,8 +1315,8 @@
       <c r="E28" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <v>6.5</v>
+      <c r="F28" s="9" t="n">
+        <v>0.7</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1329,7 +1325,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>5.0-8.0</t>
+          <t>ratio=0.69 (0.44-1.25)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1356,17 +1352,17 @@
       <c r="E29" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="11" t="n">
-        <v>4.2</v>
+      <c r="F29" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>3.5-5.0</t>
+          <t>ratio=0.88 (0.75-1.67)</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1393,17 +1389,17 @@
       <c r="E30" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="11" t="n">
-        <v>4.5</v>
+      <c r="F30" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>4.0-5.0</t>
+          <t>ratio=0.79 (0.61-1.06)</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1428,17 +1424,15 @@
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
-      <c r="F31" s="9" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1465,8 +1459,8 @@
       <c r="E32" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>0.8</v>
+      <c r="F32" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1475,7 +1469,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.00 (0.50-2.00)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1519,8 +1513,8 @@
       <c r="E34" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="9" t="n">
-        <v>1.5</v>
+      <c r="F34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1529,7 +1523,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-25.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1554,17 +1548,15 @@
         </is>
       </c>
       <c r="E35" s="8" t="n"/>
-      <c r="F35" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1589,17 +1581,15 @@
         </is>
       </c>
       <c r="E36" s="8" t="n"/>
-      <c r="F36" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>global:2.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1627,12 +1617,12 @@
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1676,8 +1666,8 @@
       <c r="E39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>2.8</v>
+      <c r="F39" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1686,7 +1676,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=3.00 (0.50-5.00)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1713,8 +1703,8 @@
       <c r="E40" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>8.4</v>
+      <c r="F40" s="9" t="n">
+        <v>1.5</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1723,7 +1713,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>4.0-12.0</t>
+          <t>ratio=0.75 (0.50-1.71)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1751,12 +1741,12 @@
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1784,12 +1774,12 @@
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1816,8 +1806,8 @@
       <c r="E43" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>4</v>
+      <c r="F43" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1826,7 +1816,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>3.0-7.0</t>
+          <t>ratio=1.00 (1.00-1.25)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1854,12 +1844,12 @@
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1887,12 +1877,12 @@
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1920,12 +1910,12 @@
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1969,8 +1959,8 @@
       <c r="E48" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>6</v>
+      <c r="F48" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1979,7 +1969,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>3.0-8.0</t>
+          <t>ratio=3.00 (2.00-4.00)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2007,12 +1997,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2039,8 +2029,8 @@
       <c r="E50" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>3</v>
+      <c r="F50" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2049,7 +2039,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>2.0-8.5</t>
+          <t>ratio=2.50 (1.50-4.00)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2063,7 +2053,7 @@
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>110.4</v>
+        <v>41.6</v>
       </c>
     </row>
   </sheetData>
@@ -2131,7 +2121,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-109, 25-034, 25-097, 25-096, 25-094</t>
+          <t>23-057, 23-059, 23-058, 25-010, 23-061</t>
         </is>
       </c>
     </row>
@@ -3333,35 +3323,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-109</t>
+          <t>23-057</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-034</t>
+          <t>23-059</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-097</t>
+          <t>23-058</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-096</t>
+          <t>25-010</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-094</t>
+          <t>23-061</t>
         </is>
       </c>
     </row>
@@ -3416,23 +3406,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3450,19 +3436,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>25-034, 25-094, 25-096, 25-097, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3476,7 +3458,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3485,12 +3467,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (0.50-1.33)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3488,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3515,12 +3497,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.0-6.0</t>
+          <t>ratio=1.00 (0.71-1.50)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3518,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3545,12 +3527,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.5-8.0</t>
+          <t>ratio=0.80 (0.62-1.21)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3566,21 +3548,21 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.8-4.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3578,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3605,12 +3587,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.0-3.0</t>
+          <t>ratio=1.00 (1.00-1.10)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094</t>
+          <t>23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3617,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-097, 25-096, 25-094, 25-034</t>
+          <t>23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3638,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3665,12 +3647,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6.0-6.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-034</t>
+          <t>23-061</t>
         </is>
       </c>
     </row>
@@ -3690,19 +3672,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>25-096, 25-097, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3716,7 +3694,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3725,12 +3703,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>global:1.0-64.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3724,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3755,12 +3733,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>global:1.0-74.2</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -3780,17 +3758,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-109, 25-094, 25-034</t>
+          <t>23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3806,23 +3784,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3836,21 +3810,21 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>global:0.5-114.5</t>
+          <t>ratio=1.17 (1.00-1.17)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>23-061, 23-059, 23-058</t>
         </is>
       </c>
     </row>
@@ -3866,21 +3840,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=0.83 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-094, 25-034</t>
+          <t>25-010, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3870,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.5</v>
+        <v>0.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3905,12 +3879,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5.0-8.0</t>
+          <t>ratio=0.69 (0.44-1.25)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3926,21 +3900,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.5-5.0</t>
+          <t>ratio=0.88 (0.75-1.67)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-109, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3956,21 +3930,21 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4.0-5.0</t>
+          <t>ratio=0.79 (0.61-1.06)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-109, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -3986,23 +3960,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>global:0.5-2.0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4016,7 +3986,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4025,12 +3995,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.00 (0.50-2.00)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4016,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,12 +4025,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>global:0.5-25.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -4076,23 +4046,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4106,23 +4072,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>global:2.0-2.0</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4140,19 +4102,15 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>25-096, 25-097, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4166,7 +4124,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4175,12 +4133,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=3.00 (0.50-5.00)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4154,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4205,12 +4163,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4.0-12.0</t>
+          <t>ratio=0.75 (0.50-1.71)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -4230,19 +4188,15 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>25-034, 25-094, 25-096, 25-097, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4260,19 +4214,15 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>25-096, 25-097, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4286,7 +4236,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4295,12 +4245,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3.0-7.0</t>
+          <t>ratio=1.00 (1.00-1.25)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -4320,19 +4270,15 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>25-034, 25-094, 25-096, 25-097, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4350,12 +4296,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -4376,12 +4322,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>no data</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -4398,7 +4344,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4407,12 +4353,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.0-8.0</t>
+          <t>ratio=3.00 (2.00-4.00)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>
@@ -4432,19 +4378,15 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>25-034, 25-094, 25-096, 25-097, 25-109</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4458,7 +4400,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4467,12 +4409,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2.0-8.5</t>
+          <t>ratio=2.50 (1.50-4.00)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-109, 25-097, 25-096, 25-094, 25-034</t>
+          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-076 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-076 GENERATED BUILD PLAN.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-057, 23-059, 23-058, 25-010, 23-061</t>
+          <t>23-057, 23-059, 25-010, 23-061, 23-058</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-057, 23-059, 23-058, 25-010, 23-061</t>
+          <t>23-057, 23-059, 25-010, 23-061, 23-058</t>
         </is>
       </c>
     </row>
@@ -3337,21 +3337,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>23-058</t>
+          <t>25-010</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-010</t>
+          <t>23-061</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-061</t>
+          <t>23-058</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-076 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-076 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -78,18 +78,6 @@
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -109,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,8 +110,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +529,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-057, 23-059, 25-010, 23-061, 23-058</t>
+          <t>23-057, 23-059, 25-012, 23-058, 25-010</t>
         </is>
       </c>
     </row>
@@ -638,12 +624,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +657,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +716,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +744,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +753,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.71-1.50)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -812,7 +798,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -821,7 +807,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.62-1.21)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -848,17 +834,17 @@
       <c r="E13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="10" t="n">
+      <c r="F13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -903,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -912,7 +898,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.10)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -957,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -966,7 +952,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -993,17 +979,17 @@
       <c r="E18" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="11" t="n">
-        <v>2</v>
+      <c r="F18" s="9" t="n">
+        <v>3.6</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1048,12 +1034,12 @@
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1080,17 +1066,17 @@
       <c r="E21" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>3</v>
+      <c r="F21" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1117,17 +1103,17 @@
       <c r="E22" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <v>2</v>
+      <c r="F22" s="9" t="n">
+        <v>4.1</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1155,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1164,7 +1150,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1192,12 +1178,12 @@
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1225,7 +1211,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1234,7 +1220,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (1.00-1.17)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1279,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1288,7 +1274,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.50-1.00)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1316,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1325,7 +1311,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.69 (0.44-1.25)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1353,7 +1339,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1362,7 +1348,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-1.67)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1390,7 +1376,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1399,7 +1385,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.79 (0.61-1.06)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1427,12 +1413,12 @@
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1460,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1469,7 +1455,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-2.00)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1513,17 +1499,17 @@
       <c r="E34" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="10" t="n">
-        <v>1</v>
+      <c r="F34" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1551,12 +1537,12 @@
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1584,12 +1570,12 @@
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1617,12 +1603,12 @@
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1667,7 +1653,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1676,7 +1662,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.00 (0.50-5.00)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1704,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1713,7 +1699,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.71)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1741,12 +1727,12 @@
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1774,12 +1760,12 @@
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1807,7 +1793,7 @@
         <v>5</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1816,7 +1802,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.25)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1844,12 +1830,12 @@
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1877,12 +1863,12 @@
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1910,12 +1896,12 @@
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1960,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1969,7 +1955,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-4.00)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -1997,12 +1983,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2030,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2039,7 +2025,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.50-4.00)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2053,7 +2039,7 @@
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>41.6</v>
+        <v>71.3</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2107,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>23-057, 23-059, 25-010, 23-061, 23-058</t>
+          <t>23-057, 23-059, 25-012, 23-058, 25-010</t>
         </is>
       </c>
     </row>
@@ -3337,21 +3323,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-010</t>
+          <t>25-012</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-061</t>
+          <t>23-058</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23-058</t>
+          <t>25-010</t>
         </is>
       </c>
     </row>
@@ -3410,15 +3396,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3436,15 +3426,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3458,7 +3452,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3467,12 +3461,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.33)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3482,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3497,12 +3491,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.71-1.50)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3512,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3527,12 +3521,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.62-1.21)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3552,17 +3546,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3572,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3587,12 +3581,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.10)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23-061, 23-059, 23-058, 23-057</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3602,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3617,12 +3611,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>23-061, 23-059, 23-058, 23-057</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -3638,21 +3632,21 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>23-061</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -3672,15 +3666,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3694,21 +3692,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -3724,21 +3722,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3752,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3763,12 +3761,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23-059, 23-058, 23-057</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -3788,15 +3786,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3810,7 +3812,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3819,12 +3821,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.17 (1.00-1.17)</t>
+          <t>group_total:17h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>23-061, 23-059, 23-058</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3842,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3849,12 +3851,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.50-1.00)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-010, 23-059, 23-058, 23-057</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3872,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3879,12 +3881,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=0.69 (0.44-1.25)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>23-061, 23-059, 23-058, 23-057</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3902,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3909,12 +3911,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.75-1.67)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3932,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.4</v>
+        <v>4.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,12 +3941,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=0.79 (0.61-1.06)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -3964,15 +3966,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3986,7 +3992,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,12 +4001,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-2.00)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4016,21 +4022,21 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4050,15 +4056,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4076,15 +4086,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4102,15 +4116,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4124,7 +4142,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4133,12 +4151,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=3.00 (0.50-5.00)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>23-061, 23-059, 23-058, 23-057</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4172,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4163,12 +4181,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.71)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4188,15 +4206,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4214,15 +4236,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4236,7 +4262,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4245,12 +4271,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.25)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4270,15 +4296,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4296,15 +4326,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4322,15 +4356,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4344,7 +4382,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4353,12 +4391,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-4.00)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4378,15 +4416,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4400,7 +4442,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4409,12 +4451,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.50-4.00)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-010, 23-061, 23-059, 23-058, 23-057</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-076 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-076 GENERATED BUILD PLAN.xlsx
@@ -744,7 +744,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -835,7 +835,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -889,7 +889,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -943,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -980,7 +980,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1067,7 +1067,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1104,7 +1104,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1141,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1211,7 +1211,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1265,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1302,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1339,7 +1339,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1376,7 +1376,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1446,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1653,7 +1653,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1690,7 +1690,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1793,7 +1793,7 @@
         <v>5</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1946,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2016,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>71.3</v>
+        <v>67.7</v>
       </c>
     </row>
   </sheetData>
@@ -3482,7 +3482,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:5h</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:6h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:17h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4022,7 +4022,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:16h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4142,7 +4142,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>group_total:12h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
